--- a/data/trans_orig/P1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Clase-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>80455</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -836,57 +836,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71637</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>80455</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>80455</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>80455</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -953,47 +953,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>68687</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1066,57 +1066,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67485</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>68687</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>68687</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>68687</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1183,47 +1183,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>58245</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,57 +1296,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83944</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>58245</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>58245</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>58245</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>83944</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,47 +1413,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>151296</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1526,57 +1526,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148562</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151296</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>151296</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>151296</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1643,47 +1643,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69123</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1756,57 +1756,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>84530</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>69123</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>69123</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>69123</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>84530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1873,47 +1873,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1986,57 +1986,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2103,47 +2103,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>745</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>502675</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2216,57 +2216,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>745</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>502675</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>502675</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>502675</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2399,7 +2399,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2567,47 +2567,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>61221</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -2680,57 +2680,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73410</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>61221</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>61221</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>61221</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2797,47 +2797,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>65379</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2910,57 +2910,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68526</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>65379</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>65379</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>65379</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3027,47 +3027,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>66523</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3140,57 +3140,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67964</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>66523</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>66523</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>66523</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67964</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3257,47 +3257,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136480</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3370,57 +3370,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161364</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136480</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>136480</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>136480</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>161364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3487,47 +3487,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>93451</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3600,57 +3600,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>92008</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>93451</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>93451</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>93451</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>92008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3717,47 +3717,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3830,57 +3830,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3947,47 +3947,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4060,57 +4060,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>537310</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>537310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4243,7 +4243,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4411,47 +4411,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>64831</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -4524,57 +4524,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78254</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>64831</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>64831</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>64831</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4641,47 +4641,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>82311</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -4754,57 +4754,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>82311</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>82311</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>82311</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4871,47 +4871,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>49224</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4984,57 +4984,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>49224</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>49224</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>49224</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5101,47 +5101,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>165797</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -5214,57 +5214,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>170883</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165797</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>165797</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165797</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>170883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5331,47 +5331,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>101579</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -5444,57 +5444,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>101579</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>101579</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>101579</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>99153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5561,47 +5561,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>60334</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5674,57 +5674,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>60334</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>60334</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>60334</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5791,47 +5791,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>524076</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -5904,57 +5904,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>570192</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>524076</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>524076</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>524076</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>570192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6087,7 +6087,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6255,47 +6255,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6368,57 +6368,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6443,17 +6443,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6485,47 +6485,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -6598,57 +6598,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6673,17 +6673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6715,47 +6715,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -6828,57 +6828,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6903,17 +6903,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6945,47 +6945,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>218825</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>437097</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -7058,57 +7058,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>218825</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>218825</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>218825</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7133,17 +7133,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>437097</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>437097</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437097</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7175,47 +7175,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -7288,57 +7288,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7363,17 +7363,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7405,47 +7405,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -7518,57 +7518,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7635,47 +7635,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>689387</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>930</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>658153</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>749225</t>
+          <t>621702</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1407378</t>
+          <t>1311090</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -7748,57 +7748,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689387</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>689387</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>689387</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>930</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>658153</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>658153</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>658153</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>749225</t>
+          <t>621702</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>749225</t>
+          <t>621702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>749225</t>
+          <t>621702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7823,17 +7823,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1407378</t>
+          <t>1311090</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1407378</t>
+          <t>1311090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1407378</t>
+          <t>1311090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
